--- a/Paper/_output/_comparison/detector_evaluation.xlsx
+++ b/Paper/_output/_comparison/detector_evaluation.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -576,25 +576,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>360</v>
+        <v>159</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.7601880877742947</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3564695801199657</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.4991689750692521</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2" t="b">
         <v>0</v>
@@ -636,22 +636,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-147</v>
+        <v>153</v>
       </c>
       <c r="G3" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>514</v>
+        <v>360</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0.7613814756671899</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.6170421155729677</v>
+        <v>0.3559176672384219</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.7158430232558139</v>
+        <v>0.4991680532445923</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -695,25 +695,29 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>-147</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="H4" t="n">
+        <v>514</v>
+      </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.6170421155729677</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>0.7158430232558139</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -751,36 +755,32 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>16</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>452</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" s="2" t="n">
-        <v>0.3478260869565217</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
         <v>1</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.8770491803278688</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -812,25 +812,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-457</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-193</v>
+        <v>452</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.005128205128205128</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3710691823899371</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2319688109161793</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -872,23 +872,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-34</v>
+        <v>-457</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>457</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-193</v>
+      </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.005128205128205128</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.3710691823899371</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>0.2319688109161793</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -898,7 +900,7 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -911,12 +913,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -926,29 +928,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-3</v>
+        <v>-34</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.280564263322884</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.03427592116538132</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1213296398891967</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -986,29 +986,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>66</v>
+        <v>-16</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.8619718309859155</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1939275220372184</v>
+        <v>0.4406779661016949</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3662790697674418</v>
+        <v>0.3</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
@@ -1046,29 +1046,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>-4</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.765625</v>
+        <v>0.2794348508634223</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.03430531732418525</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0.1209095951192457</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
@@ -1106,29 +1106,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8619718309859155</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5858585858585859</v>
+        <v>0.1939275220372184</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.6311475409836066</v>
+        <v>0.3662790697674418</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -1166,29 +1166,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.8923076923076924</v>
+        <v>0.7538461538461538</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.456140350877193</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.5631067961165048</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1286,29 +1286,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-50</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.6630094043887147</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.1705227077977721</v>
+        <v>0.1886792452830189</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.3445983379501385</v>
+        <v>0.456140350877193</v>
       </c>
       <c r="L14" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1346,29 +1346,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.8563380281690141</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3192948090107737</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.4578488372093023</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="L15" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
@@ -1406,29 +1406,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>210</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.71875</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.2839506172839506</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.4758620689655172</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-7</v>
+        <v>-51</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="H17" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0.6624803767660911</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.1706689536878216</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.8852459016393442</v>
+        <v>0.3444259567387687</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -1526,29 +1526,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-23</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8563380281690141</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2987421383647799</v>
+        <v>0.3192948090107737</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.50682261208577</v>
+        <v>0.4578488372093023</v>
       </c>
       <c r="L18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.5681818181818182</v>
+        <v>0.4726027397260274</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
@@ -1626,46 +1626,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>applied</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>156</v>
+        <v>-7</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.7570532915360502</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3538988860325621</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.496398891966759</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1680,59 +1680,55 @@
       <c r="P20" t="b">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>13</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>applied</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-131</v>
+        <v>-23</v>
       </c>
       <c r="G21" t="n">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="H21" t="n">
-        <v>523</v>
+        <v>44</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6327130264446621</v>
+        <v>0.2987421383647799</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.50682261208577</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
@@ -1744,58 +1740,58 @@
       <c r="P21" t="b">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>16</v>
-      </c>
-      <c r="R21" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>applied</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>13</v>
+      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>29</v>
+      </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>0.509090909090909</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -1830,7 +1826,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1842,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9292929292929293</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1857,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1888,26 +1884,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-442</v>
+        <v>155</v>
       </c>
       <c r="G24" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-174</v>
+        <v>373</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.7582417582417582</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3867924528301887</v>
+        <v>0.3533447684391081</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1923,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -1952,27 +1948,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-114</v>
+        <v>-131</v>
       </c>
       <c r="G25" t="n">
-        <v>114</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="H25" t="n">
+        <v>523</v>
+      </c>
       <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>0.6327130264446621</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
@@ -1982,12 +1980,14 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-80</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="R25" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2012,32 +2012,28 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>156</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="n">
-        <v>18</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.1786833855799373</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.03341902313624678</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.08476454293628809</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2046,12 +2042,8 @@
       <c r="P26" t="b">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>159</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2061,12 +2053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2076,46 +2068,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>39</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="n">
-        <v>81</v>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="n">
-        <v>0.7183098591549296</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2017629774730656</v>
+        <v>0.9320388349514563</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8</v>
+      </c>
       <c r="P27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>29</v>
-      </c>
-      <c r="R27" t="n">
-        <v>15</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2125,12 +2111,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2140,29 +2126,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>-442</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="H28" t="n">
-        <v>46</v>
+        <v>-174</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.546875</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.3867924528301887</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -2178,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="R28" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -2189,12 +2175,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2204,29 +2190,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-10</v>
+        <v>-114</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" t="n">
-        <v>49</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7070707070707071</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.7622950819672131</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
@@ -2236,14 +2220,12 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>-15</v>
-      </c>
-      <c r="R29" t="n">
-        <v>16</v>
-      </c>
+        <v>-80</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2268,46 +2250,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>-21</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>21</v>
-      </c>
-      <c r="H30" t="n">
-        <v>77</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="n">
-        <v>0.8974358974358975</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2389937106918239</v>
+        <v>0.7288135593220338</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
       <c r="P30" t="b">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>-25</v>
-      </c>
-      <c r="R30" t="n">
-        <v>47</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2332,29 +2308,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.1789638932496075</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.03344768439108062</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
@@ -2367,10 +2343,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2381,12 +2357,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2396,29 +2372,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-35</v>
+        <v>39</v>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.7084639498432602</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1748071979434447</v>
+        <v>0.2017629774730656</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="L32" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -2431,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
+        <v>29</v>
+      </c>
+      <c r="R32" t="n">
         <v>15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="33">
@@ -2445,12 +2421,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2460,29 +2436,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.7746478873239436</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2644466209598433</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="L33" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -2495,10 +2471,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -2509,12 +2485,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2524,29 +2500,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.546875</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3209876543209876</v>
+        <v>0.6796116504854369</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -2559,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>-15</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -2573,12 +2549,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2588,29 +2564,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>-21</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H35" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9292929292929293</v>
+        <v>0.2389937106918239</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -2623,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>-25</v>
       </c>
       <c r="R35" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -2637,12 +2613,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2652,29 +2628,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-21</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.882051282051282</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2987421383647799</v>
+        <v>0.2909090909090909</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.52046783625731</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -2687,10 +2663,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2716,29 +2692,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H37" t="n">
-        <v>38</v>
+        <v>317</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.1470588235294118</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6851851851851852</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
@@ -2751,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>-56</v>
       </c>
       <c r="R37" t="n">
-        <v>9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38">
@@ -2765,44 +2741,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>197</v>
+        <v>-36</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H38" t="n">
-        <v>373</v>
+        <v>141</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.6927899686520376</v>
+        <v>0.7080062794348508</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3538988860325621</v>
+        <v>0.1749571183533448</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -2815,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="R38" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39">
@@ -2829,44 +2805,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-131</v>
+        <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>523</v>
+        <v>103</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>0.7746478873239436</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.633692458374143</v>
+        <v>0.2644466209598433</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -2879,10 +2855,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -2893,44 +2869,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-120</v>
+        <v>31</v>
       </c>
       <c r="G40" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-57</v>
+        <v>27</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.09375</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0</v>
+        <v>0.3209876543209876</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -2942,8 +2918,12 @@
       <c r="P40" t="b">
         <v>0</v>
       </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>11</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2953,55 +2933,61 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>93</v>
+      </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9292929292929293</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.8492063492063492</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="b">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>16</v>
+      </c>
+      <c r="R41" t="n">
         <v>8</v>
       </c>
-      <c r="P41" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3011,44 +2997,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-442</v>
+        <v>-21</v>
       </c>
       <c r="G42" t="n">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="H42" t="n">
-        <v>-132</v>
+        <v>77</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.3179487179487179</v>
+        <v>0.882051282051282</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.389937106918239</v>
+        <v>0.2987421383647799</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.52046783625731</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -3061,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
@@ -3075,42 +3061,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-94</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
-        <v>94</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>38</v>
+      </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -3120,12 +3108,14 @@
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>-60</v>
-      </c>
-      <c r="R43" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="R43" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3135,12 +3125,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3153,43 +3143,37 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>259</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="n">
-        <v>59</v>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.2084639498432602</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.04970008568980291</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.1058171745152355</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="L44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="b">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>23</v>
+      </c>
       <c r="P44" t="b">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>262</v>
-      </c>
-      <c r="R44" t="n">
-        <v>41</v>
-      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3199,12 +3183,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3218,25 +3202,25 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-43</v>
+        <v>373</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.7126760563380282</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.1841332027424094</v>
+        <v>0.3533447684391081</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -3249,10 +3233,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="R45" t="n">
-        <v>-109</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -3263,12 +3247,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3281,37 +3265,43 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>-131</v>
+      </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="H46" t="n">
+        <v>523</v>
+      </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.633692458374143</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="b">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="b">
         <v>0</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>16</v>
+      </c>
+      <c r="R46" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3321,12 +3311,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3339,32 +3329,34 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>-119</v>
+      </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-57</v>
+      </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.9292929292929293</v>
+        <v>0</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="b">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="b">
         <v>0</v>
       </c>
@@ -3379,12 +3371,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3397,43 +3389,37 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>63</v>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="n">
-        <v>119</v>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" s="2" t="n">
-        <v>0.6820512820512821</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3710691823899371</v>
+        <v>0.9320388349514563</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>8</v>
+      </c>
       <c r="P48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>59</v>
-      </c>
-      <c r="R48" t="n">
-        <v>89</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3443,12 +3429,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3462,25 +3448,25 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-30</v>
+        <v>-442</v>
       </c>
       <c r="G49" t="n">
-        <v>30</v>
+        <v>442</v>
       </c>
       <c r="H49" t="n">
-        <v>58</v>
+        <v>-132</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0.3179487179487179</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1</v>
+        <v>0.389937106918239</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -3493,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>-39</v>
+        <v>15</v>
       </c>
       <c r="R49" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
@@ -3507,12 +3493,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3522,29 +3508,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>-94</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>183</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>0.5047021943573667</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.209083119108826</v>
+        <v>1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.313573407202216</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -3554,14 +3538,12 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>58</v>
-      </c>
-      <c r="R50" t="n">
-        <v>154</v>
-      </c>
+        <v>-60</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3571,12 +3553,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3586,46 +3568,40 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>59</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="n">
-        <v>145</v>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.8366197183098592</v>
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.327130264446621</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.4585755813953488</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="L51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>23</v>
+      </c>
       <c r="P51" t="b">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>40</v>
-      </c>
-      <c r="R51" t="n">
-        <v>49</v>
-      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3635,12 +3611,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3650,40 +3626,46 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>258</v>
+      </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>59</v>
+      </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>0.2087912087912088</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.04974271012006861</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>0.1059345535219079</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="b">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="b">
         <v>0</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>262</v>
+      </c>
+      <c r="R52" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3693,12 +3675,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3708,40 +3690,46 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>59</v>
+      </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>-43</v>
+      </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>0.7126760563380282</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9292929292929293</v>
+        <v>0.1841332027424094</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="b">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="b">
         <v>0</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>49</v>
+      </c>
+      <c r="R53" t="n">
+        <v>-109</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3751,12 +3739,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3766,46 +3754,40 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>-63</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>63</v>
-      </c>
-      <c r="H54" t="n">
-        <v>181</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.7530864197530864</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.4178082191780822</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="b">
         <v>1</v>
       </c>
-      <c r="J54" s="2" t="n">
-        <v>0.5660377358490566</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>0.7309941520467836</v>
-      </c>
-      <c r="L54" t="n">
+      <c r="N54" t="b">
         <v>1</v>
       </c>
-      <c r="M54" t="b">
-        <v>0</v>
-      </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>6</v>
+      </c>
       <c r="P54" t="b">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>-40</v>
-      </c>
-      <c r="R54" t="n">
-        <v>137</v>
-      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3815,12 +3797,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3830,46 +3812,40 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>-94</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>94</v>
-      </c>
-      <c r="H55" t="n">
-        <v>58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.9320388349514563</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="L55" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="M55" t="b">
         <v>1</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="N55" t="b">
         <v>1</v>
       </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="b">
-        <v>0</v>
-      </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>8</v>
+      </c>
       <c r="P55" t="b">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>-107</v>
-      </c>
-      <c r="R55" t="n">
-        <v>29</v>
-      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3879,41 +3855,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>563</v>
+        <v>119</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.6927899686520376</v>
+        <v>0.6820512820512821</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4815766923736076</v>
+        <v>0.3710691823899371</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.5562326869806095</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="L56" t="n">
         <v>2</v>
@@ -3929,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="R56" t="n">
-        <v>203</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57">
@@ -3943,44 +3919,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H57" t="n">
-        <v>963</v>
+        <v>58</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.8366197183098592</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9422135161606269</v>
+        <v>1</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.9149709302325582</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -3993,10 +3969,10 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>206</v>
+        <v>-39</v>
       </c>
       <c r="R57" t="n">
-        <v>449</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58">
@@ -4007,43 +3983,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>-10</v>
+      </c>
       <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H58" t="n">
+        <v>339</v>
+      </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -4052,8 +4032,12 @@
       <c r="P58" t="b">
         <v>0</v>
       </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="Q58" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R58" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4063,43 +4047,47 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>7</v>
+      </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>183</v>
+      </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>0.5054945054945055</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0</v>
+        <v>0.20926243567753</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -4108,8 +4096,12 @@
       <c r="P59" t="b">
         <v>0</v>
       </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>58</v>
+      </c>
+      <c r="R59" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4119,44 +4111,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-251</v>
+        <v>59</v>
       </c>
       <c r="G60" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>307</v>
+        <v>145</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0.8366197183098592</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9622641509433962</v>
+        <v>0.327130264446621</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -4169,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="R60" t="n">
-        <v>500</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61">
@@ -4183,56 +4175,54 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.7530864197530864</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.4178082191780822</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" t="b">
         <v>1</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="N61" t="b">
         <v>1</v>
       </c>
-      <c r="K61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="b">
-        <v>0</v>
-      </c>
-      <c r="N61" t="b">
-        <v>0</v>
-      </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>6</v>
+      </c>
       <c r="P61" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4243,22 +4233,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -4270,21 +4260,23 @@
         <v>0</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0</v>
+        <v>0.9320388349514563</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="b">
         <v>1</v>
       </c>
       <c r="N62" t="b">
-        <v>0</v>
-      </c>
-      <c r="O62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>8</v>
+      </c>
       <c r="P62" t="b">
         <v>0</v>
       </c>
@@ -4299,44 +4291,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>59</v>
+        <v>-63</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H63" t="n">
-        <v>-43</v>
+        <v>181</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.7126760563380282</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2448579823702253</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.3655523255813953</v>
+        <v>0.7309941520467836</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -4349,10 +4341,10 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>49</v>
+        <v>-40</v>
       </c>
       <c r="R63" t="n">
-        <v>-109</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64">
@@ -4363,55 +4355,61 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>-94</v>
+      </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="H64" t="n">
+        <v>58</v>
+      </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9382716049382716</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
-      </c>
-      <c r="O64" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="b">
         <v>0</v>
       </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
+      <c r="Q64" t="n">
+        <v>-107</v>
+      </c>
+      <c r="R64" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4421,12 +4419,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4436,7 +4434,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -4477,12 +4475,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4492,40 +4490,46 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>196</v>
+      </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>563</v>
+      </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7861635220125787</v>
+        <v>0.4819897084048028</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="b">
         <v>0</v>
       </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="Q66" t="n">
+        <v>43</v>
+      </c>
+      <c r="R66" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4535,12 +4539,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4550,27 +4554,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-30</v>
+        <v>59</v>
       </c>
       <c r="G67" t="n">
-        <v>30</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>963</v>
+      </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>0.8366197183098592</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1</v>
+        <v>0.9422135161606269</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -4580,12 +4586,14 @@
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>-39</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="R67" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4595,12 +4603,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4610,32 +4618,28 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>197</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="n">
-        <v>-193</v>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" s="2" t="n">
-        <v>0.3887147335423197</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2159383033419023</v>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.2770083102493075</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4644,12 +4648,8 @@
       <c r="P68" t="b">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>247</v>
-      </c>
-      <c r="R68" t="n">
-        <v>-222</v>
-      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4674,32 +4674,28 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>59</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="n">
-        <v>209</v>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" s="2" t="n">
-        <v>0.8366197183098592</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2037218413320274</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.3670058139534884</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4708,12 +4704,8 @@
       <c r="P69" t="b">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>40</v>
-      </c>
-      <c r="R69" t="n">
-        <v>113</v>
-      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4723,12 +4715,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4738,40 +4730,46 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>-251</v>
+      </c>
       <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="H70" t="n">
+        <v>307</v>
+      </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9382716049382716</v>
+        <v>0.9622641509433962</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
-      </c>
-      <c r="O70" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="b">
         <v>0</v>
       </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="Q70" t="n">
+        <v>206</v>
+      </c>
+      <c r="R70" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4781,12 +4779,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4796,37 +4794,41 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>-30</v>
+      </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>4</v>
+      </c>
       <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -4837,12 +4839,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4852,32 +4854,28 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="b">
         <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>307</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>0.9622641509433962</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>0.9766081871345029</v>
-      </c>
-      <c r="L72" t="n">
-        <v>2</v>
-      </c>
-      <c r="M72" t="b">
-        <v>0</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4886,12 +4884,8 @@
       <c r="P72" t="b">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>24</v>
-      </c>
-      <c r="R72" t="n">
-        <v>263</v>
-      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4901,12 +4895,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4916,42 +4910,764 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>-30</v>
-      </c>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="b">
         <v>1</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="b">
-        <v>0</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>59</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0.7126760563380282</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.2448579823702253</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.3655523255813953</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>49</v>
+      </c>
+      <c r="R74" t="n">
+        <v>-109</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.9382716049382716</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="L75" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>6</v>
+      </c>
+      <c r="P75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.7861635220125787</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.4873294346978557</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" t="b">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>57</v>
+      </c>
+      <c r="P77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G78" t="n">
+        <v>30</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>-39</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>-134</v>
+      </c>
+      <c r="G79" t="n">
+        <v>134</v>
+      </c>
+      <c r="H79" t="n">
+        <v>339</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-138</v>
+      </c>
+      <c r="R79" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>196</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-193</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0.3893249607535322</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.2161234991423671</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.2773155851358846</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>247</v>
+      </c>
+      <c r="R80" t="n">
+        <v>-222</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>59</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>209</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0.8366197183098592</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.2037218413320274</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0.3670058139534884</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>40</v>
+      </c>
+      <c r="R81" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.9382716049382716</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="b">
+        <v>1</v>
+      </c>
+      <c r="N82" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>6</v>
+      </c>
+      <c r="P82" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>1</v>
+      </c>
+      <c r="N83" t="b">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>307</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.9622641509433962</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>24</v>
+      </c>
+      <c r="R84" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G85" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
         <v>-43</v>
       </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5158,52 +5874,52 @@
         <v>199.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>399</v>
+        <v>232</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.1162926260565433</v>
+        <v>0.06761877003788982</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2573593704459342</v>
+        <v>0.2599825123870592</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.6745607333842628</v>
+        <v>0.6656716417910448</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.3725738396624473</v>
+        <v>0.3739258017187173</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.5776767963646692</v>
+        <v>0.5758307299062766</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4452823570676955</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.6150581444699093</v>
+        <v>0.6101946423616746</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.6412124744972312</v>
+        <v>0.6621976100262315</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5433440355643369</v>
+        <v>0.5483948829350712</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5999471877475575</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.562624254473161</v>
+        <v>0.5697245100823629</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.4112930170397595</v>
+        <v>0.3997930320800276</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.5660255092622888</v>
+        <v>0.5743009254275218</v>
       </c>
     </row>
     <row r="3">
@@ -5243,13 +5959,13 @@
         <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.2425167990226023</v>
+        <v>0.2260232131948686</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -5258,37 +5974,37 @@
         <v>0.4593769089798412</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.5744843391902216</v>
+        <v>0.5611940298507463</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.5105227427019688</v>
+        <v>0.5052065838092039</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.7952286282306164</v>
+        <v>0.7908264697529112</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1543694400837258</v>
+        <v>0.1552086987022097</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.7100574495532479</v>
+        <v>0.7029926655742682</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.7037263286499694</v>
+        <v>0.7196090409285278</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2845146949864164</v>
+        <v>0.2843350229302438</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.405205768554344</v>
+        <v>0.4076124567474049</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.5197387105935813</v>
+        <v>0.5137744958818518</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.1620447711326428</v>
+        <v>0.1583304587788893</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.5612349619268868</v>
+        <v>0.5630022820756773</v>
       </c>
     </row>
     <row r="4">
@@ -5328,52 +6044,52 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>970</v>
+        <v>672</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.335292084341514</v>
+        <v>0.232284825440719</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3397856895955755</v>
+        <v>0.3491185620463187</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.7509549274255156</v>
+        <v>0.753731343283582</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.4678724416944312</v>
+        <v>0.4772029293645168</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.6824765691564897</v>
+        <v>0.6857426867367226</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.333158904587476</v>
+        <v>0.3302350052613118</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.7088980114190198</v>
+        <v>0.7117481690111351</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.6011061182163844</v>
+        <v>0.6308330452817145</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4294887626574463</v>
+        <v>0.4405020516533912</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5010083549409393</v>
+        <v>0.5187606594656055</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.5080942913944902</v>
+        <v>0.5191706901448452</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.3855663214166388</v>
+        <v>0.3684028975508796</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.5219612206204037</v>
+        <v>0.5360495770512558</v>
       </c>
     </row>
     <row r="5">
@@ -5413,52 +6129,52 @@
         <v>230</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>397</v>
+        <v>230</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1156759906759907</v>
+        <v>0.06701631701631702</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0.2599067599067599</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.6814362108479756</v>
+        <v>0.6656716417910448</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.376291921535541</v>
+        <v>0.3738474434199497</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.5800908832717978</v>
+        <v>0.5756887247940926</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4430490144775859</v>
+        <v>0.445457734128376</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.6191935981851948</v>
+        <v>0.6101069538313344</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.6468531468531469</v>
+        <v>0.664918414918415</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.54828352679674</v>
+        <v>0.5508085928071446</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5935035423071783</v>
+        <v>0.6025082508250825</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.5681624538483385</v>
+        <v>0.5724226072138597</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.4049448713665219</v>
+        <v>0.3966885132804415</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.571669327715109</v>
+        <v>0.5770600397633515</v>
       </c>
     </row>
     <row r="6">
@@ -5498,52 +6214,52 @@
         <v>22.5</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.1690051020408163</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0.4005102040816326</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.479755538579068</v>
+        <v>0.4686567164179105</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.4365658672228016</v>
+        <v>0.4319119669876204</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.7698097131496734</v>
+        <v>0.7654075546719682</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1639630211058782</v>
+        <v>0.1648544370396352</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.6578962587365949</v>
+        <v>0.6519011396891377</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.6887755102040817</v>
+        <v>0.7161989795918368</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2667325265497654</v>
+        <v>0.2710596186338402</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3845469111625423</v>
+        <v>0.3932761337769217</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.5090883271797785</v>
+        <v>0.5079522862823062</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.163047109923154</v>
+        <v>0.1535012073128665</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.5518427083133056</v>
+        <v>0.5587792056604868</v>
       </c>
     </row>
     <row r="7">
@@ -5583,52 +6299,52 @@
         <v>42</v>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>957</v>
+        <v>557</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.342152306042188</v>
+        <v>0.1991419377904898</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3410797282803003</v>
+        <v>0.3518055058991777</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7288006111535523</v>
+        <v>0.7343283582089553</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.4646858256210424</v>
+        <v>0.4757070340826687</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.6878727634194831</v>
+        <v>0.6919909116728202</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3214721786150357</v>
+        <v>0.3179586110136794</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.7036642162692583</v>
+        <v>0.7081848735976379</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.5999284948158742</v>
+        <v>0.631748301751877</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.414423314398617</v>
+        <v>0.4265025343953657</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.4902132632193982</v>
+        <v>0.509221902017291</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.5044021584777052</v>
+        <v>0.5163305879011645</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.3738723688606749</v>
+        <v>0.3552949292859607</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.520275472768971</v>
+        <v>0.5356038025547025</v>
       </c>
     </row>
     <row r="8">
@@ -5668,52 +6384,52 @@
         <v>253</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>253</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.07318484234885739</v>
+      </c>
+      <c r="M8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>441</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0.1275672548452415</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
       <c r="N8" s="2" t="n">
-        <v>0.2600520682672838</v>
+        <v>0.2603413364188603</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6867838044308633</v>
+        <v>0.6716417910447762</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.3772555602182123</v>
+        <v>0.375234521575985</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.5785288270377733</v>
+        <v>0.5744106787844362</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4461887319030176</v>
+        <v>0.4484391441599439</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.6202975362639228</v>
+        <v>0.6116013234424161</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.644778709864044</v>
+        <v>0.6569279722302575</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5505062978513213</v>
+        <v>0.5481535119478639</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.5939248601119105</v>
+        <v>0.5976315789473684</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.5671684180630503</v>
+        <v>0.5657483669412099</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.4102906782492483</v>
+        <v>0.4091065884787858</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.5701078098010366</v>
+        <v>0.569523461734539</v>
       </c>
     </row>
     <row r="9">
@@ -5753,52 +6469,52 @@
         <v>64</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.1686507936507937</v>
+        <v>0.1263227513227513</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0.3657407407407408</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.4224598930481284</v>
+        <v>0.4126865671641791</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.3920595533498759</v>
+        <v>0.3877980364656382</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.7564612326043738</v>
+        <v>0.7520590741266686</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1672771672771673</v>
+        <v>0.168186601192564</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.6275913628854806</v>
+        <v>0.6222499829858076</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.7433862433862434</v>
+        <v>0.7711640211640212</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2775994072610521</v>
+        <v>0.2814385710837558</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.4042438410357849</v>
+        <v>0.4123784261715297</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.5295370633342801</v>
+        <v>0.5281170122124397</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.1296358169061143</v>
+        <v>0.1193515005174198</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.5739817951774689</v>
+        <v>0.581043535283168</v>
       </c>
     </row>
     <row r="10">
@@ -5850,40 +6566,40 @@
         <v>2</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.2909632571996028</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.6478227654698243</v>
+        <v>0.6559701492537313</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.3916859122401847</v>
+        <v>0.4031185507911029</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>0.6259585345072423</v>
+        <v>0.6303606929849475</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.3790336647479505</v>
+        <v>0.3756576639775517</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0.6343945503609369</v>
+        <v>0.6401562426380898</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.6001324064879179</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4477648802173376</v>
+        <v>0.4605358435916003</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.5128712871287129</v>
+        <v>0.5326633165829145</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.5109343936381709</v>
+        <v>0.5245668844078387</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.4036084196458403</v>
+        <v>0.3839254915488099</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.5220782302857487</v>
+        <v>0.5383051760213952</v>
       </c>
     </row>
     <row r="11">
@@ -5932,43 +6648,43 @@
         <v>0.06687898089171974</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0.2569002123142251</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.7394957983193278</v>
+        <v>0.7223880597014926</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0.3813275556430963</v>
+        <v>0.3790133124510571</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0.5539619426299347</v>
+        <v>0.5495597841522295</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>0.4884004884004884</v>
+        <v>0.4910557699052964</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0.6255476549594197</v>
+        <v>0.615666144898098</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.7569002123142251</v>
+        <v>0.7571656050955414</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>0.7043714497406767</v>
+        <v>0.6886314265025344</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.7296916975821927</v>
+        <v>0.7212741751990898</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.6999431979551264</v>
+        <v>0.6868787276341949</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0.3060474440360842</v>
+        <v>0.3156260779579165</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0.6991620028522962</v>
+        <v>0.6865026742723089</v>
       </c>
     </row>
     <row r="12">
@@ -6017,43 +6733,43 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0.2290502793296089</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.2192513368983957</v>
+        <v>0.2141791044776119</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.2240437158469945</v>
+        <v>0.2213652140377941</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>0.7176938369781312</v>
+        <v>0.713291678500426</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>0.1684981684981685</v>
+        <v>0.1694142406173273</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>0.5253765842001137</v>
+        <v>0.5223824319301423</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0.7318435754189944</v>
+        <v>0.7326416600159616</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0.2264756730056804</v>
+        <v>0.221578566256336</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.3459072048283667</v>
+        <v>0.3402520385470719</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.5075262709457541</v>
+        <v>0.4944618006248225</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.1122619445372536</v>
+        <v>0.115557088651259</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>0.5571068642342134</v>
+        <v>0.5530107388025385</v>
       </c>
     </row>
     <row r="13">
@@ -6105,40 +6821,40 @@
         <v>2</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.280231716147719</v>
+        <v>0.2914554670528602</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.5912910618792971</v>
+        <v>0.6007462686567164</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.3802505526897568</v>
+        <v>0.3924914675767919</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.6417211019596706</v>
+        <v>0.6461232604373758</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0.3467643467643468</v>
+        <v>0.3432129077516661</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0.6222633575574752</v>
+        <v>0.6287666804525252</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.6046343229543809</v>
+        <v>0.6375814627081825</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0.4124475179056557</v>
+        <v>0.4250543084721217</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.4903832036411687</v>
+        <v>0.510065170166546</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.5071002556092019</v>
+        <v>0.5195967054813974</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.3648513197460742</v>
+        <v>0.3452914798206278</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>0.5237980990797908</v>
+        <v>0.5398814143257469</v>
       </c>
     </row>
   </sheetData>
@@ -6251,7 +6967,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -6293,7 +7009,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -6335,7 +7051,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C1, C2</t>
+          <t>C2, C3</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -6377,7 +7093,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -6461,7 +7177,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -6503,7 +7219,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C4, C5</t>
+          <t>C5, C6</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -6545,7 +7261,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -6587,7 +7303,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -6629,7 +7345,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -6671,7 +7387,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -6713,7 +7429,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -6755,7 +7471,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -6797,7 +7513,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -6839,7 +7555,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -6881,7 +7597,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -7007,7 +7723,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -7049,7 +7765,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
@@ -7091,7 +7807,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -7133,7 +7849,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
@@ -7175,7 +7891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -7217,7 +7933,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -7259,7 +7975,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -7301,7 +8017,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -7343,7 +8059,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -7385,7 +8101,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -7427,7 +8143,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -7469,7 +8185,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
@@ -7511,7 +8227,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -7553,7 +8269,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -7595,7 +8311,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -7637,7 +8353,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
@@ -7679,7 +8395,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -7721,7 +8437,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -7763,7 +8479,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -7805,7 +8521,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -7847,7 +8563,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -7889,7 +8605,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -7931,7 +8647,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -7973,7 +8689,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
@@ -8015,7 +8731,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
@@ -8183,7 +8899,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -8225,7 +8941,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -8267,7 +8983,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -8309,7 +9025,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
@@ -8351,7 +9067,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -8393,7 +9109,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
@@ -8435,7 +9151,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -8477,7 +9193,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
@@ -8519,7 +9235,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -8561,7 +9277,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
@@ -8603,7 +9319,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
@@ -8645,7 +9361,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -8687,7 +9403,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -8729,7 +9445,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
@@ -8771,7 +9487,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -8813,7 +9529,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -8855,7 +9571,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -8897,7 +9613,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -8939,7 +9655,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -8981,7 +9697,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -10913,7 +11629,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
@@ -10955,7 +11671,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
@@ -10997,7 +11713,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
@@ -11039,7 +11755,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
@@ -11081,7 +11797,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
@@ -11123,7 +11839,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
@@ -11417,7 +12133,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
@@ -11459,7 +12175,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
@@ -11501,7 +12217,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
@@ -11543,7 +12259,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -11585,7 +12301,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
@@ -11627,7 +12343,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -11669,7 +12385,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
@@ -11711,7 +12427,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
@@ -12173,7 +12889,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
@@ -12215,7 +12931,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
@@ -12257,7 +12973,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
@@ -12299,7 +13015,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
@@ -12341,7 +13057,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
@@ -12383,7 +13099,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
@@ -12425,7 +13141,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
@@ -12467,7 +13183,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
@@ -12509,7 +13225,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
@@ -12551,7 +13267,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
@@ -12593,7 +13309,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
@@ -12761,7 +13477,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
@@ -12803,7 +13519,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
@@ -12845,7 +13561,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
@@ -12887,7 +13603,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
@@ -12929,7 +13645,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
@@ -12971,7 +13687,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
@@ -13013,7 +13729,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
@@ -13055,7 +13771,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
@@ -13097,7 +13813,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
@@ -13139,7 +13855,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
@@ -13391,7 +14107,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
@@ -13433,7 +14149,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
@@ -13601,7 +14317,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I177" s="2" t="n">
@@ -13643,7 +14359,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I178" s="2" t="n">
@@ -13685,7 +14401,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I179" s="2" t="n">
@@ -13727,7 +14443,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I180" s="2" t="n">
@@ -13769,7 +14485,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I181" s="2" t="n">
@@ -13811,7 +14527,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I182" s="2" t="n">
@@ -13853,7 +14569,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I183" s="2" t="n">
@@ -13895,7 +14611,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I184" s="2" t="n">
@@ -13937,7 +14653,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I185" s="2" t="n">
@@ -13979,7 +14695,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I186" s="2" t="n">
@@ -14021,7 +14737,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I187" s="2" t="n">
@@ -14063,7 +14779,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I188" s="2" t="n">
@@ -14105,7 +14821,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I189" s="2" t="n">
@@ -14147,7 +14863,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I190" s="2" t="n">
@@ -14189,7 +14905,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I191" s="2" t="n">
@@ -14231,7 +14947,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I192" s="2" t="n">
@@ -14273,7 +14989,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I193" s="2" t="n">
@@ -14315,7 +15031,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I194" s="2" t="n">
@@ -14357,7 +15073,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I195" s="2" t="n">
@@ -14399,7 +15115,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I196" s="2" t="n">
@@ -14441,7 +15157,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I197" s="2" t="n">
@@ -14483,7 +15199,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I198" s="2" t="n">
@@ -14525,7 +15241,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I199" s="2" t="n">
@@ -14567,7 +15283,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I200" s="2" t="n">
@@ -14609,7 +15325,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I201" s="2" t="n">
@@ -14651,7 +15367,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I202" s="2" t="n">
@@ -14693,7 +15409,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I203" s="2" t="n">
@@ -14735,7 +15451,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I204" s="2" t="n">
@@ -14777,7 +15493,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I205" s="2" t="n">
@@ -14861,7 +15577,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I207" s="2" t="n">
@@ -14903,7 +15619,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I208" s="2" t="n">
@@ -14945,7 +15661,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I209" s="2" t="n">
@@ -14987,7 +15703,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I210" s="2" t="n">
@@ -15029,7 +15745,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I211" s="2" t="n">
@@ -15071,7 +15787,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I212" s="2" t="n">
@@ -15113,7 +15829,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I213" s="2" t="n">
@@ -15155,7 +15871,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I214" s="2" t="n">
@@ -15197,7 +15913,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I215" s="2" t="n">
@@ -15239,7 +15955,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I216" s="2" t="n">
@@ -15281,7 +15997,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I217" s="2" t="n">
@@ -15323,7 +16039,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I218" s="2" t="n">
@@ -15365,7 +16081,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I219" s="2" t="n">
@@ -15407,7 +16123,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I220" s="2" t="n">
@@ -15449,7 +16165,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I221" s="2" t="n">
@@ -15491,7 +16207,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I222" s="2" t="n">
@@ -15533,7 +16249,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I223" s="2" t="n">
@@ -15575,7 +16291,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I224" s="2" t="n">
@@ -16289,7 +17005,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I241" s="2" t="n">
@@ -16457,7 +17173,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I245" s="2" t="n">
@@ -16499,7 +17215,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I246" s="2" t="n">
@@ -16877,7 +17593,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I255" s="2" t="n">
@@ -16919,7 +17635,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I256" s="2" t="n">
@@ -16961,7 +17677,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I257" s="2" t="n">
@@ -17003,7 +17719,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I258" s="2" t="n">
@@ -17045,7 +17761,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I259" s="2" t="n">
@@ -17087,7 +17803,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I260" s="2" t="n">
@@ -17129,7 +17845,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I261" s="2" t="n">
@@ -17171,7 +17887,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I262" s="2" t="n">
@@ -17213,7 +17929,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I263" s="2" t="n">
@@ -17255,7 +17971,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I264" s="2" t="n">
@@ -17297,7 +18013,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I265" s="2" t="n">
@@ -17339,7 +18055,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I266" s="2" t="n">
@@ -17381,7 +18097,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I267" s="2" t="n">
@@ -17423,7 +18139,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I268" s="2" t="n">
@@ -17465,7 +18181,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I269" s="2" t="n">
@@ -17507,7 +18223,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I270" s="2" t="n">
@@ -17591,7 +18307,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I272" s="2" t="n">
@@ -17633,7 +18349,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I273" s="2" t="n">
@@ -17675,7 +18391,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I274" s="2" t="n">
@@ -17717,7 +18433,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I275" s="2" t="n">
@@ -17843,7 +18559,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I278" s="2" t="n">
@@ -17885,7 +18601,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I279" s="2" t="n">
@@ -17927,7 +18643,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>C1, C2</t>
+          <t>C2, C3</t>
         </is>
       </c>
       <c r="I280" s="2" t="n">
@@ -17969,7 +18685,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I281" s="2" t="n">
@@ -18053,7 +18769,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I283" s="2" t="n">
@@ -18095,7 +18811,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>C4, C5</t>
+          <t>C5, C6</t>
         </is>
       </c>
       <c r="I284" s="2" t="n">
@@ -18137,7 +18853,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I285" s="2" t="n">
@@ -18179,7 +18895,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I286" s="2" t="n">
@@ -18221,7 +18937,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I287" s="2" t="n">
@@ -18263,7 +18979,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I288" s="2" t="n">
@@ -18305,7 +19021,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I289" s="2" t="n">
@@ -18347,7 +19063,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I290" s="2" t="n">
@@ -18389,7 +19105,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I291" s="2" t="n">
@@ -18431,7 +19147,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I292" s="2" t="n">
@@ -18473,7 +19189,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I293" s="2" t="n">
@@ -18515,7 +19231,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I294" s="2" t="n">
@@ -18557,7 +19273,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I295" s="2" t="n">
@@ -18599,7 +19315,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I296" s="2" t="n">
@@ -18641,7 +19357,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I297" s="2" t="n">
@@ -18683,7 +19399,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I298" s="2" t="n">
@@ -18725,7 +19441,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I299" s="2" t="n">
@@ -19061,7 +19777,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I307" s="2" t="n">
@@ -19103,7 +19819,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I308" s="2" t="n">
@@ -19229,7 +19945,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I311" s="2" t="n">
@@ -19271,7 +19987,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I312" s="2" t="n">
@@ -19397,7 +20113,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I315" s="2" t="n">
@@ -19439,7 +20155,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I316" s="2" t="n">
@@ -19481,7 +20197,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I317" s="2" t="n">
@@ -19523,7 +20239,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I318" s="2" t="n">
@@ -19607,7 +20323,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I320" s="2" t="n">
@@ -19649,7 +20365,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I321" s="2" t="n">
@@ -19691,7 +20407,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I322" s="2" t="n">
@@ -19733,7 +20449,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I323" s="2" t="n">
@@ -19775,7 +20491,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I324" s="2" t="n">
@@ -19817,7 +20533,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I325" s="2" t="n">
@@ -19859,7 +20575,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I326" s="2" t="n">
@@ -19901,7 +20617,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I327" s="2" t="n">
@@ -19943,7 +20659,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I328" s="2" t="n">
@@ -19985,7 +20701,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I329" s="2" t="n">
@@ -20027,7 +20743,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I330" s="2" t="n">
@@ -20069,7 +20785,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I331" s="2" t="n">
@@ -20111,7 +20827,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I332" s="2" t="n">
@@ -20153,7 +20869,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I333" s="2" t="n">
@@ -20195,7 +20911,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I334" s="2" t="n">
@@ -20237,7 +20953,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I335" s="2" t="n">
@@ -20279,7 +20995,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I336" s="2" t="n">
@@ -20657,7 +21373,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I345" s="2" t="n">
@@ -20783,7 +21499,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I348" s="2" t="n">
@@ -20951,7 +21667,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I352" s="2" t="n">
@@ -20993,7 +21709,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I353" s="2" t="n">
@@ -21035,7 +21751,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I354" s="2" t="n">
@@ -21077,7 +21793,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I355" s="2" t="n">
@@ -21161,7 +21877,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I357" s="2" t="n">
@@ -21203,7 +21919,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I358" s="2" t="n">
@@ -21287,7 +22003,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I360" s="2" t="n">
@@ -21329,7 +22045,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I361" s="2" t="n">
@@ -21371,7 +22087,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>C1, C2</t>
+          <t>C2, C3</t>
         </is>
       </c>
       <c r="I362" s="2" t="n">
@@ -21413,7 +22129,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I363" s="2" t="n">
@@ -21497,7 +22213,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I365" s="2" t="n">
@@ -21539,7 +22255,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>C4, C5</t>
+          <t>C5, C6</t>
         </is>
       </c>
       <c r="I366" s="2" t="n">
@@ -21581,7 +22297,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I367" s="2" t="n">
@@ -21623,7 +22339,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I368" s="2" t="n">
@@ -21665,7 +22381,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>false_alarm</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I369" s="2" t="n">
@@ -21707,7 +22423,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I370" s="2" t="n">
@@ -21749,7 +22465,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I371" s="2" t="n">
@@ -21791,7 +22507,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I372" s="2" t="n">
@@ -21833,7 +22549,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I373" s="2" t="n">
@@ -21875,7 +22591,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I374" s="2" t="n">
@@ -21917,7 +22633,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I375" s="2" t="n">
@@ -22085,7 +22801,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I379" s="2" t="n">
@@ -22127,7 +22843,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I380" s="2" t="n">
@@ -22169,7 +22885,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I381" s="2" t="n">
@@ -22211,7 +22927,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I382" s="2" t="n">
@@ -22253,7 +22969,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I383" s="2" t="n">
@@ -22337,7 +23053,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C1, C2</t>
         </is>
       </c>
       <c r="I385" s="2" t="n">
@@ -22379,7 +23095,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I386" s="2" t="n">
@@ -22421,7 +23137,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I387" s="2" t="n">
@@ -22463,7 +23179,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I388" s="2" t="n">
@@ -22505,7 +23221,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I389" s="2" t="n">
@@ -22547,7 +23263,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I390" s="2" t="n">
@@ -22589,7 +23305,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I391" s="2" t="n">
@@ -22631,7 +23347,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I392" s="2" t="n">
@@ -22673,7 +23389,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I393" s="2" t="n">
@@ -22715,7 +23431,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I394" s="2" t="n">
@@ -22757,7 +23473,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I395" s="2" t="n">
@@ -22925,7 +23641,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I399" s="2" t="n">
@@ -22967,7 +23683,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I400" s="2" t="n">
@@ -23009,7 +23725,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I401" s="2" t="n">
@@ -23093,7 +23809,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I403" s="2" t="n">
@@ -23135,7 +23851,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I404" s="2" t="n">
@@ -23177,7 +23893,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I405" s="2" t="n">
@@ -23219,7 +23935,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I406" s="2" t="n">
@@ -23261,7 +23977,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I407" s="2" t="n">
@@ -23345,7 +24061,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I409" s="2" t="n">
@@ -23387,7 +24103,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I410" s="2" t="n">
@@ -23429,7 +24145,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I411" s="2" t="n">
@@ -23471,7 +24187,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I412" s="2" t="n">
@@ -23513,7 +24229,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>C3, C4</t>
+          <t>C4, C5</t>
         </is>
       </c>
       <c r="I413" s="2" t="n">
@@ -23555,7 +24271,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I414" s="2" t="n">
@@ -23597,7 +24313,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I415" s="2" t="n">
@@ -23639,7 +24355,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C1, C2</t>
         </is>
       </c>
       <c r="I416" s="2" t="n">
@@ -23681,7 +24397,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I417" s="2" t="n">
@@ -23723,7 +24439,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I418" s="2" t="n">
@@ -23765,7 +24481,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I419" s="2" t="n">
@@ -23849,7 +24565,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>C3, C4</t>
+          <t>C4, C5</t>
         </is>
       </c>
       <c r="I421" s="2" t="n">
@@ -23891,7 +24607,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I422" s="2" t="n">
@@ -23933,7 +24649,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I423" s="2" t="n">
@@ -24019,7 +24735,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>missed: never defensive peak -&gt; trough. late_defensive: missed, but defensive trough -&gt; break-even. still_defensive_at_end: no break from the switch to the next crisis peak (C6: end of the data).</t>
+          <t>missed: never defensive peak -&gt; trough. late_defensive: missed, but defensive trough -&gt; break-even. still_defensive_at_end: no break from the switch to the next crisis peak (C7: end of the data).</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24763,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C6 is censored at the end of the data (2025-12-31).</t>
+          <t>C7 is censored at the end of the data (2025-12-31).</t>
         </is>
       </c>
     </row>
